--- a/templates/revenue-stream-template.xlsx
+++ b/templates/revenue-stream-template.xlsx
@@ -546,13 +546,13 @@
     <t>Unique VIN VAS  for the  day</t>
   </si>
   <si>
-    <t>Total Car Care Treatments Target(w/o Mech Care)</t>
+    <t>Total Car Care Treatments Target</t>
   </si>
   <si>
-    <t>Total Car Care Treatments  for the  day(w/o Mech Care)</t>
+    <t>Total Car Care Treatments  for the  day</t>
   </si>
   <si>
-    <t>Achvmnt for the month(w/o Mech Care)</t>
+    <t>Achvmnt for the month</t>
   </si>
   <si>
     <t>TP-TP Target</t>
